--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FA71AD-6D38-4683-9B2F-B4F3810B1B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1D1BBE-CB8B-4A72-920F-E4F9334B160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Ranking!$A$1:$I$13</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Nombre</t>
   </si>
@@ -98,6 +111,9 @@
   </si>
   <si>
     <t>Jare</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -133,8 +149,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,136 +492,212 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.875" customWidth="1"/>
     <col min="2" max="9" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="1">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>-B176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1D1BBE-CB8B-4A72-920F-E4F9334B160A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC71608-18F1-4781-95AA-25081B9D4EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Nombre</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Jare</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -503,201 +500,127 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <v>46287</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>65</v>
-      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
-        <f>-B176</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
-        <v>7</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B20">
-        <v>8</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
-        <v>9</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="B22" s="2"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
-        <v>9</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
-      </c>
-      <c r="B25">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC71608-18F1-4781-95AA-25081B9D4EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038DCB4-FF52-42E1-AA0E-98995865D685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Nombre</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>Jare</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -149,7 +155,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,134 +508,207 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1">
+        <v>46287</v>
+      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1 B22" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038DCB4-FF52-42E1-AA0E-98995865D685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89134FD8-EFB7-4029-9DF9-1335B953CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>Nombre</t>
   </si>
@@ -497,210 +497,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.875" customWidth="1"/>
     <col min="2" max="9" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
         <v>46287</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89134FD8-EFB7-4029-9DF9-1335B953CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4692F-F21B-429F-9C12-B8E46F8E4B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t>Nombre</t>
   </si>
@@ -497,14 +497,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.875" customWidth="1"/>
     <col min="2" max="9" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,8 +514,11 @@
       <c r="C1" s="1">
         <v>46289</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -525,8 +528,11 @@
       <c r="C2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -536,8 +542,11 @@
       <c r="C3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -547,8 +556,11 @@
       <c r="C4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -558,8 +570,11 @@
       <c r="C5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -569,8 +584,11 @@
       <c r="C6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -580,8 +598,11 @@
       <c r="C7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -591,8 +612,11 @@
       <c r="C8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -602,8 +626,11 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -613,8 +640,11 @@
       <c r="C10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -624,8 +654,11 @@
       <c r="C11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -635,8 +668,11 @@
       <c r="C12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -646,8 +682,11 @@
       <c r="C13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -657,8 +696,11 @@
       <c r="C14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -668,8 +710,11 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -679,8 +724,11 @@
       <c r="C16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -690,8 +738,11 @@
       <c r="C17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -701,8 +752,11 @@
       <c r="C18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -712,8 +766,11 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -723,8 +780,11 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -734,8 +794,11 @@
       <c r="C21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -745,8 +808,11 @@
       <c r="C22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -756,8 +822,11 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -767,8 +836,11 @@
       <c r="C24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -776,6 +848,9 @@
         <v>25</v>
       </c>
       <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4692F-F21B-429F-9C12-B8E46F8E4B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A560509A-1B93-4BE8-8EAB-0C17E9431668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
   <si>
     <t>Nombre</t>
   </si>
@@ -497,14 +497,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.875" customWidth="1"/>
     <col min="2" max="9" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,8 +517,11 @@
       <c r="D1" s="1">
         <v>46290</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -531,8 +534,14 @@
       <c r="D2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -545,8 +554,14 @@
       <c r="D3">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -559,8 +574,14 @@
       <c r="D4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -573,8 +594,14 @@
       <c r="D5">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -587,8 +614,14 @@
       <c r="D6">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -601,8 +634,14 @@
       <c r="D7">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -615,8 +654,14 @@
       <c r="D8">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -629,8 +674,14 @@
       <c r="D9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -643,8 +694,14 @@
       <c r="D10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -657,8 +714,14 @@
       <c r="D11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -671,8 +734,14 @@
       <c r="D12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -685,8 +754,14 @@
       <c r="D13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -699,8 +774,14 @@
       <c r="D14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -713,8 +794,14 @@
       <c r="D15">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -727,8 +814,14 @@
       <c r="D16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -741,8 +834,14 @@
       <c r="D17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -755,8 +854,14 @@
       <c r="D18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -769,8 +874,14 @@
       <c r="D19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -783,8 +894,14 @@
       <c r="D20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -797,8 +914,14 @@
       <c r="D21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -811,8 +934,14 @@
       <c r="D22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -825,8 +954,14 @@
       <c r="D23">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -839,8 +974,14 @@
       <c r="D24">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -851,6 +992,12 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/ranking.xlsx
+++ b/data/ranking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvalle\Desktop\PhD\Ranking_competi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A560509A-1B93-4BE8-8EAB-0C17E9431668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BA9FC0-FBF5-4E75-89B3-E0C85E2987F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30960" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -520,6 +520,9 @@
       <c r="E1" s="1">
         <v>46304</v>
       </c>
+      <c r="F1" s="1">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
